--- a/AutoXP3_samples_split/Sample2.xlsx
+++ b/AutoXP3_samples_split/Sample2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Downloads\AutoXP3_samples_split\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Dropbox\claude\AutoXP3_samples_split\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9007DBA3-4A0D-4E26-8D35-B6B84BA92B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848216DA-61A1-47DB-BCD8-7EACE16CB866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Definition" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
     <t>Y1</t>
   </si>
   <si>
-    <t>&gt;0</t>
+    <t>&gt;</t>
   </si>
   <si>
     <t>id</t>
@@ -83,44 +83,363 @@
     <t>True model</t>
   </si>
   <si>
-    <t>Y1 = 1.5*X1 + 2.0*X2 + 0.5</t>
-  </si>
-  <si>
     <t>Optimal condition</t>
   </si>
   <si>
-    <t>X1 = 10, X2 = 10</t>
+    <t>X1=9, X2=10 (max Y1=36.7)</t>
+  </si>
+  <si>
+    <t>Y1 = 3.6*X1 + 2.0*X2 - 0.2*X1^2  + 0.5</t>
+    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="游ゴシック Light"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -128,18 +447,293 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - アクセント 1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="アクセント 1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="アクセント 2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="アクセント 3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="アクセント 4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="アクセント 5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="アクセント 6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="タイトル" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="チェック セル" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="どちらでもない" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="メモ" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="リンク セル" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="悪い" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="計算" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="見出し 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="見出し 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="見出し 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="見出し 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="集計" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="出力" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="説明文" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="入力" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="良い" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -152,7 +746,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -162,44 +756,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -226,14 +820,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -260,6 +872,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -271,175 +901,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -462,7 +1068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -473,7 +1079,7 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -482,7 +1088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -502,7 +1108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -514,17 +1120,17 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -538,151 +1144,283 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="D2">
-        <v>0.58162257703906706</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>26.819179999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5.62</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="D3">
-        <v>2.0009373711634781</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>18.375119999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>5.72</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="D4">
-        <v>5.4563675688799407</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>20.148319999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>6.23</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D5">
-        <v>7.0511608408314448</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>24.36542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2.48</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>4.97</v>
       </c>
       <c r="D6">
-        <v>10.52367379933507</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>18.137920000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>3.74</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>5.13</v>
       </c>
       <c r="D7">
-        <v>11.950101268272491</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>21.426480000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>5.31</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="D8">
-        <v>15.581949251193651</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>19.776779999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>2.97</v>
       </c>
       <c r="D9">
-        <f>1.5*B9+2*C9+0.5</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>13.55448</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>3.84</v>
       </c>
       <c r="D10">
-        <f>1.5*B10+2*C10+0.2</f>
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>14.49582</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
+        <v>7.19</v>
+      </c>
+      <c r="C11">
+        <v>4.05</v>
+      </c>
+      <c r="D11">
+        <v>24.144780000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f>3.6*B12-0.2*B12^2+2*C12+0.5</f>
+        <v>-7.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ref="D13:D17" si="0">3.6*B13-0.2*B13^2+2*C13+0.5</f>
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <f>3.6*B14-0.2*B14^2+2*C14+0.5</f>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="C11">
-        <v>5</v>
-      </c>
-      <c r="D11">
-        <f>1.5*B11+2*C11+0.8</f>
-        <v>12.3</v>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>34.900000000000006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <f t="shared" ref="D18:D20" si="1">3.6*B18-0.2*B18^2+2*C18+0.5</f>
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>34.900000000000006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>36.5</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -690,9 +1428,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="11.9140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -700,24 +1441,24 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>